--- a/artfynd/A 18606-2026 artfynd.xlsx
+++ b/artfynd/A 18606-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126514301</v>
+        <v>126513970</v>
       </c>
       <c r="B2" t="n">
-        <v>80084</v>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435853</v>
+        <v>435750</v>
       </c>
       <c r="R2" t="n">
-        <v>6962772</v>
+        <v>6962709</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126514300</v>
+        <v>126514301</v>
       </c>
       <c r="B3" t="n">
-        <v>98278</v>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435856</v>
+        <v>435853</v>
       </c>
       <c r="R3" t="n">
-        <v>6962781</v>
+        <v>6962772</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,6 +870,208 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126513971</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Båthustjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>435735</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6962733</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126514300</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Båthustjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>435856</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6962781</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 18606-2026 artfynd.xlsx
+++ b/artfynd/A 18606-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126513970</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126514301</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126513971</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,8 +1096,19 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126514300</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>